--- a/data_raw/data_raw_2024_sheets/LTER1_BR_P03_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER1_BR_P03_2024.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73357FC9-CEF4-A743-BE95-8047CB693F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625E4A2B-31B9-7F42-A3E4-DCF61A05D4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="500" windowWidth="28900" windowHeight="23500" xr2:uid="{23A7D850-3B1A-6244-8337-BB35CA056BA3}"/>
+    <workbookView xWindow="1000" yWindow="560" windowWidth="28900" windowHeight="18780" xr2:uid="{23A7D850-3B1A-6244-8337-BB35CA056BA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="30">
   <si>
     <t>LTER1</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>Mssing data</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>HL</t>
@@ -203,30 +200,6 @@
   </cellStyles>
   <dxfs count="19">
     <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -258,6 +231,30 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
         </patternFill>
       </fill>
     </dxf>
@@ -348,6 +345,20 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <sz val="11"/>
         <color rgb="FF000000"/>
@@ -368,20 +379,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -715,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C8287A-17DE-B14E-B7DA-C16259B3FF26}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
@@ -743,7 +740,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -851,7 +848,7 @@
         <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -877,10 +874,10 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -897,19 +894,28 @@
         <v>5</v>
       </c>
       <c r="E6" s="6">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F6">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6">
         <v>6</v>
       </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -926,28 +932,19 @@
         <v>5</v>
       </c>
       <c r="E7" s="6">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F7">
+        <v>36</v>
+      </c>
+      <c r="G7">
         <v>35</v>
       </c>
-      <c r="G7">
-        <v>40</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
+      <c r="H7" t="s">
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -964,19 +961,28 @@
         <v>5</v>
       </c>
       <c r="E8" s="6">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>8</v>
+      </c>
+      <c r="J8">
+        <v>7.5</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -990,31 +996,22 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9">
-        <v>7.5</v>
-      </c>
-      <c r="K9">
-        <v>6</v>
-      </c>
       <c r="L9" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -1028,22 +1025,31 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" s="6">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>25</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>7</v>
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -1060,25 +1066,25 @@
         <v>5</v>
       </c>
       <c r="E11" s="6">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>4</v>
@@ -1098,10 +1104,10 @@
         <v>5</v>
       </c>
       <c r="E12" s="6">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G12">
         <v>20</v>
@@ -1110,13 +1116,13 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L12" t="s">
         <v>4</v>
@@ -1136,25 +1142,25 @@
         <v>5</v>
       </c>
       <c r="E13" s="6">
-        <v>2.17</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F13">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>25</v>
       </c>
       <c r="J13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
         <v>4</v>
@@ -1177,19 +1183,19 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F14">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>29.5</v>
       </c>
       <c r="J14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K14">
         <v>18</v>
@@ -1212,19 +1218,19 @@
         <v>5</v>
       </c>
       <c r="E15" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="J15">
         <v>23</v>
@@ -1247,28 +1253,28 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="6">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F16">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
         <v>4</v>
       </c>
       <c r="I16">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="J16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L16" t="s">
         <v>4</v>
@@ -1285,28 +1291,28 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="6">
         <v>2.6</v>
       </c>
       <c r="F17">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G17">
-        <v>30</v>
-      </c>
-      <c r="H17" t="s">
-        <v>4</v>
+        <v>40</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>28.5</v>
+        <v>4.2</v>
       </c>
       <c r="J17">
-        <v>22</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L17" t="s">
         <v>4</v>
@@ -1323,22 +1329,22 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E18" s="6">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="F18">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G18">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I18">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J18">
         <v>3.5</v>
@@ -1361,28 +1367,28 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="6">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="F19">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I19">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J19">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" t="s">
         <v>4</v>
@@ -1399,31 +1405,22 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E20" s="6">
         <v>2.65</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I20">
-        <v>4</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20">
-        <v>3</v>
-      </c>
       <c r="L20" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -1437,22 +1434,31 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6">
         <v>2.65</v>
       </c>
       <c r="F21">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="G21">
-        <v>35</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>28.5</v>
+      </c>
+      <c r="J21">
+        <v>27</v>
+      </c>
+      <c r="K21">
+        <v>13</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -1466,31 +1472,22 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E22" s="6">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="F22">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
         <v>4</v>
       </c>
-      <c r="I22">
-        <v>28.5</v>
-      </c>
-      <c r="J22">
-        <v>27</v>
-      </c>
-      <c r="K22">
-        <v>13</v>
-      </c>
       <c r="L22" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -1504,22 +1501,22 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23" s="6">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="F23">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H23" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -1536,19 +1533,28 @@
         <v>5</v>
       </c>
       <c r="E24" s="6">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="F24">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G24">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24">
         <v>26</v>
       </c>
+      <c r="J24">
+        <v>21</v>
+      </c>
+      <c r="K24">
+        <v>19</v>
+      </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -1562,28 +1568,28 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="6">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="F25">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="G25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H25" t="s">
         <v>4</v>
       </c>
       <c r="I25">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J25">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="L25" t="s">
         <v>4</v>
@@ -1600,28 +1606,28 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F26">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s">
         <v>4</v>
       </c>
       <c r="I26">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="J26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K26">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="L26" t="s">
         <v>4</v>
@@ -1641,28 +1647,28 @@
         <v>5</v>
       </c>
       <c r="E27" s="6">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="F27">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G27">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
         <v>4</v>
       </c>
       <c r="I27">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K27">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -1682,25 +1688,25 @@
         <v>3.05</v>
       </c>
       <c r="F28">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G28">
         <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>36</v>
+        <v>27.5</v>
       </c>
       <c r="J28">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K28">
-        <v>26</v>
+        <v>20.5</v>
       </c>
       <c r="L28" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -1717,28 +1723,19 @@
         <v>5</v>
       </c>
       <c r="E29" s="6">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="F29">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="G29">
-        <v>40</v>
-      </c>
-      <c r="H29" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29">
-        <v>27.5</v>
-      </c>
-      <c r="J29">
-        <v>26</v>
-      </c>
-      <c r="K29">
-        <v>20.5</v>
+        <v>2</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -1758,13 +1755,13 @@
         <v>3.15</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G30">
-        <v>2</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="H30" t="s">
+        <v>4</v>
       </c>
       <c r="L30" t="s">
         <v>29</v>
@@ -1784,19 +1781,28 @@
         <v>5</v>
       </c>
       <c r="E31" s="6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="F31">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>40</v>
-      </c>
-      <c r="H31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31">
+        <v>3.5</v>
+      </c>
+      <c r="J31">
+        <v>3.5</v>
+      </c>
+      <c r="K31">
         <v>4</v>
       </c>
       <c r="L31" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -1813,28 +1819,19 @@
         <v>5</v>
       </c>
       <c r="E32" s="6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I32">
-        <v>3.5</v>
-      </c>
-      <c r="J32">
-        <v>3.5</v>
-      </c>
-      <c r="K32">
-        <v>4</v>
-      </c>
       <c r="L32" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -1851,7 +1848,7 @@
         <v>5</v>
       </c>
       <c r="E33" s="6">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="F33">
         <v>73</v>
@@ -1863,7 +1860,7 @@
         <v>7</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -1880,19 +1877,19 @@
         <v>5</v>
       </c>
       <c r="E34" s="6">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="F34">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="G34">
-        <v>40</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>6</v>
       </c>
       <c r="L34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -1906,22 +1903,22 @@
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" s="6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="F35">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>6</v>
+        <v>35</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -1935,22 +1932,22 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E36" s="6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="F36">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="G36">
-        <v>35</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="H36" t="s">
+        <v>4</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -1964,22 +1961,22 @@
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E37" s="6">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="F37">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="G37">
-        <v>10</v>
-      </c>
-      <c r="H37" t="s">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -1993,22 +1990,22 @@
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E38" s="6">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="F38">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="G38">
         <v>30</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>7</v>
+      <c r="H38" t="s">
+        <v>4</v>
       </c>
       <c r="L38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -2025,19 +2022,19 @@
         <v>8</v>
       </c>
       <c r="E39" s="6">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G39">
         <v>30</v>
       </c>
-      <c r="H39" t="s">
-        <v>4</v>
+      <c r="H39" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="L39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -2051,22 +2048,22 @@
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E40" s="6">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="G40">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -2083,19 +2080,19 @@
         <v>5</v>
       </c>
       <c r="E41" s="6">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="F41">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G41">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -2112,19 +2109,19 @@
         <v>5</v>
       </c>
       <c r="E42" s="6">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="F42">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -2141,19 +2138,25 @@
         <v>5</v>
       </c>
       <c r="E43" s="6">
-        <v>3.71</v>
+        <v>0.35</v>
       </c>
       <c r="F43">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="G43">
-        <v>5</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -2170,10 +2173,10 @@
         <v>5</v>
       </c>
       <c r="E44" s="6">
-        <v>0.35</v>
+        <v>0.95</v>
       </c>
       <c r="F44">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -2202,25 +2205,25 @@
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E45" s="6">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="F45">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L45" t="s">
         <v>25</v>
@@ -2237,10 +2240,10 @@
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E46" s="6">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="F46">
         <v>10</v>
@@ -2249,10 +2252,10 @@
         <v>20</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="K46">
         <v>1.5</v>
@@ -2275,22 +2278,22 @@
         <v>5</v>
       </c>
       <c r="E47" s="6">
-        <v>0.95</v>
+        <v>2.9</v>
       </c>
       <c r="F47">
         <v>10</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="s">
         <v>25</v>
@@ -2310,19 +2313,19 @@
         <v>5</v>
       </c>
       <c r="E48" s="6">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="G48">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -2331,56 +2334,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="6">
-        <v>3.8</v>
-      </c>
-      <c r="F49">
-        <v>85</v>
-      </c>
-      <c r="G49">
-        <v>40</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="J49">
-        <v>1</v>
-      </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="L49" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="A43:C48 A3:H5">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>A3="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="2">
+      <formula>A3="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:H2">
-    <cfRule type="beginsWith" dxfId="18" priority="10" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="16" priority="10" operator="beginsWith" text="FI">
       <formula>LEFT(A2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="15" priority="11" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H6 A7:G7 A8:H8 A9:G10 A18:G38 H22:H29 H31 H35 H37 A39:H39 A40:G43 I3:K3 I7:K7 I9:K9 A11:K17 I18:K20 I22:K22 I25:K29 I32:K32 D44:G45 I44:K48 D46:D49 F46:G49 I49:I51 J49:K49">
-    <cfRule type="expression" dxfId="16" priority="12">
-      <formula>A3="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:M2">
@@ -2391,7 +2359,7 @@
       <formula>LEFT(A2,LEN("FU"))="FU"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H6 H8 H11:H17 H22:H29 H31 H35 H37 H39 I25:K29 I32:K32">
+  <conditionalFormatting sqref="H7 H10:H16 H21:H28 I24:K28 H30 I31:K31 H34 H36 H38 H3:H5">
     <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text=",">
       <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
     </cfRule>
@@ -2411,29 +2379,29 @@
       <formula>H3="Recruitment"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I3:K3 A6:G6 I6:K6 A7:H7 I8:K8 A8:G9 A10:K16 I17:K19 A17:G37 I21:K21 H21:H28 I24:K28 H30 I31:K31 H34 H36 A38:H38 A39:G42 D43:G44 I43:K47 D45:D48 F45:G48 J48:K48 I48:I50">
+    <cfRule type="expression" dxfId="6" priority="12">
+      <formula>A3="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="13">
+      <formula>A3="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="beginsWith" dxfId="6" priority="4" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="4" priority="4" operator="beginsWith" text="FI">
       <formula>LEFT(I2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",I2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="4" priority="6" operator="beginsWith" text="R">
+    <cfRule type="beginsWith" dxfId="2" priority="6" operator="beginsWith" text="R">
       <formula>LEFT(I2,LEN("R"))="R"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="D">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",I2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A44:C49">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>A44="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>A44="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
